--- a/quality_surveys/001_wildlife_management_strategy_survey--quality_surveys.xlsx
+++ b/quality_surveys/001_wildlife_management_strategy_survey--quality_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1925,17 +1925,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>policy_15_choices</t>
+          <t>policy_16_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>policy_14b</t>
+          <t>policy_15a</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Policy 14b</t>
+          <t>Policy 15a</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>policy_15a</t>
+          <t>policy_15b</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Policy 15a</t>
+          <t>Policy 15b</t>
         </is>
       </c>
     </row>
@@ -1964,29 +1964,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>policy_15b</t>
+          <t>policy_15c</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Policy 15b</t>
+          <t>Policy 15c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>policy_16_choices</t>
+          <t>policy_17_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>policy_15c</t>
+          <t>policy_16a</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Policy 15c</t>
+          <t>Policy 16a</t>
         </is>
       </c>
     </row>
@@ -1998,46 +1998,46 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>policy_16a</t>
+          <t>policy_16b</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Policy 16a</t>
+          <t>Policy 16b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>policy_17_choices</t>
+          <t>policy_18_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>policy_16b</t>
+          <t>policy_17a</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Policy 16b</t>
+          <t>Policy 17a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>policy_17_choices</t>
+          <t>policy_18_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>policy_16b</t>
+          <t>policy_17b</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Policy 16b</t>
+          <t>Policy 17b</t>
         </is>
       </c>
     </row>
@@ -2049,248 +2049,180 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>policy_17a</t>
+          <t>policy_17c</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Policy 17a</t>
+          <t>Policy 17c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>policy_18_choices</t>
+          <t>policy_19_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>policy_17b</t>
+          <t>policy_18a</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Policy 17b</t>
+          <t>Policy 18a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>policy_18_choices</t>
+          <t>policy_19_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>policy_17c</t>
+          <t>policy_18b</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Policy 17c</t>
+          <t>Policy 18b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>policy_19_choices</t>
+          <t>policy_20_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>policy_18a</t>
+          <t>policy_19a</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Policy 18a</t>
+          <t>Policy 19a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>policy_19_choices</t>
+          <t>policy_20_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>policy_18b</t>
+          <t>policy_19b</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Policy 18b</t>
+          <t>Policy 19b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>policy_19_choices</t>
+          <t>policy_20_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>policy_18b</t>
+          <t>policy_19c</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Policy 18b</t>
+          <t>Policy 19c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>policy_20_choices</t>
+          <t>policy_21_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>policy_19a</t>
+          <t>policy_20a</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Policy 19a</t>
+          <t>Policy 20a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>policy_20_choices</t>
+          <t>policy_21_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>policy_19b</t>
+          <t>policy_20b</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Policy 19b</t>
+          <t>Policy 20b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>policy_20_choices</t>
+          <t>policy_22_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>policy_19c</t>
+          <t>policy_21a</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Policy 19c</t>
+          <t>Policy 21a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>policy_21_choices</t>
+          <t>policy_22_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>policy_20a</t>
+          <t>policy_21b</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Policy 20a</t>
+          <t>Policy 21b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>policy_21_choices</t>
+          <t>policy_22_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>policy_20b</t>
+          <t>policy_21c</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
-        <is>
-          <t>Policy 20b</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>policy_21_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>policy_20b</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Policy 20b</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>policy_22_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>policy_21a</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Policy 21a</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>policy_22_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>policy_21b</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Policy 21b</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>policy_22_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>policy_21c</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
         <is>
           <t>Policy 21c</t>
         </is>
